--- a/Mod_Korean/Lang/KR/Dialog/Drama/loytel.xlsx
+++ b/Mod_Korean/Lang/KR/Dialog/Drama/loytel.xlsx
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">Why!</t>
   </si>
   <si>
-    <t xml:space="preserve">考えても見ろ。この竜は黄金を食べるんだろう？そんな竜を、貧乏な我々がどうやって養うというのだ？</t>
+    <t xml:space="preserve">考えてもみろ。この竜は黄金を食べるんだろう？そんな竜を、貧乏な我々がどうやって養うというのだ？</t>
   </si>
   <si>
     <t xml:space="preserve">Think about it. This dragon eats gold, doesn’t it? How are we supposed to feed it when we are hardly wealthy?</t>
@@ -5165,7 +5165,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
       <alignment/>
       <protection locked="1"/>
@@ -5288,10 +5288,6 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
       <protection locked="1"/>
     </xf>
   </cellXfs>
@@ -13827,7 +13823,7 @@
       <c r="I686" s="1">
         <v>411</v>
       </c>
-      <c r="J686" s="31" t="s">
+      <c r="J686" s="7" t="s">
         <v>784</v>
       </c>
       <c r="K686" s="4" t="s">

--- a/Mod_Korean/Lang/KR/Dialog/Drama/loytel.xlsx
+++ b/Mod_Korean/Lang/KR/Dialog/Drama/loytel.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="1160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2115" uniqueCount="1218">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -1371,7 +1371,7 @@
 「#pcさん、私たちを見捨てないで…！」</t>
   </si>
   <si>
-    <t xml:space="preserve">...But, I can hear it. The voice of these decayed rocks and withered soil whispering of past glories.
+    <t xml:space="preserve">...But, I can hear it. The voice of these decayed pebbles and withered soil whispering of past glories.
 "#pc, Vernis is not over yet..."
 "#pc, I can still make it..."
 "#pc, don't abandon us...!"</t>
@@ -3810,6 +3810,205 @@
     <t xml:space="preserve">key_exile</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">quest_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">stone_dream</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">stone_dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふぅ、これだけ拠点が大きくなると、帳簿を付けるだけでも一苦労だ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whew, now that our settlement has grown this large, keeping the books is becoming quite a task.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">だが、こういう地味な仕事ほど、誰かがきちんとやらねばな。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still, it's precisely the sort of mundane work that someone must see to properly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">家畜の餌に、肥料、研磨剤、耐火ブランケット、魔法書代と。
+修繕費は、訓練木人が二体、鍋、三つ。フライパン、二つ、ジョウロ…四つ？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Livestock feed, fertilizer, polishing powders, fireproof blankets, spellbook expenses...
+And for repairs, let's see: two training dummies, three cooking pots, two frying pans, and... four watering cans?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…四つ？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Four?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…犯人は明白だな。備品損耗、と。うむ、これでいい。
+ついでにコルゴンの食費も…必要……経費……と……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...The culprit is obvious. "Equipment wear and tear," then. Hmm, that will do.
+And Corgon's food expenses while I'm at it... a... necessary... expenditure...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うーん…眠い。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mmm... I'm getting sleepy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（むにゅ…むにゃ…）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Mnh... mngh...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（すや…すや…）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Zzz... zzz...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…さん…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Sir...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…ロイテル…さん…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Sir Loytel...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（すや…すや…ぅう……）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Zzz... zzz... nnh......)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…やれるよ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...I can make it...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ロイテルさん…ボクはまだやれるよ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sir Loytel... I can still make it...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ロイテルさん、私たちを見捨てないで…！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sir Loytel...Don't abandon us...!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（う…ウウウ…）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Nn... Nnngh...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pebble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボクたちを使って…ボクたちはまだやれるよ！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use us... We can still make it!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ロイテルさん、私たちを輝かせて！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sir Loytel, make us shine!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（ウウウ…！）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Nnngh...!)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（ハッ…！）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Haah...!)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">はぁ…はぁ…私としたことが、仕事中に眠ってしまったのか。
+それにしても、妙にリアルな夢だった。まるで、石ころが本当に耳元で囁いているかのような…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haah... haah... To think that I would fall asleep in the middle of my work.
+Even so, that dream felt strangely real. It was almost as though the pebbles themselves were truly whispering into my ear...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">お疲れのようですね、ロイテル様。うたた寝なさっていたのですか？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You seem tired, Lord Loytel. Were you taking a little nap?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ファリスさん…あなたは、そこで何を…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lady Farris... What were you doing there...?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">何も。ただ、小石たちの切なる声に耳を傾けていただけです。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing at all. I was merely listening to the earnest voices of the pebbles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…小石は喋りません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">But pebbles do not speak...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">では、夢だったのでしょう…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Then it must have been a dream...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（夢…だったのかな…？）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(A dream... was it...?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reward_stone_dream</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
@@ -5005,7 +5204,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -5116,6 +5315,13 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ ゴシック;Noto Sans JP;游ゴシック;メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -5165,7 +5371,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
       <alignment/>
       <protection locked="1"/>
@@ -5288,6 +5494,10 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
       <protection locked="1"/>
     </xf>
   </cellXfs>
@@ -5488,7 +5698,7 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N709"/>
+  <dimension ref="A1:N758"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
   <cols>
     <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
@@ -5544,7 +5754,7 @@
     <row r="2" ht="12.8">
       <c r="I2" s="1">
         <f>MAX(I4:I1048576)</f>
-        <v>425</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5" ht="12.8">
@@ -5568,7 +5778,7 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>814</v>
+        <v>872</v>
       </c>
     </row>
     <row r="9" ht="12.8">
@@ -5592,7 +5802,7 @@
         <v>19</v>
       </c>
       <c r="L10" t="s">
-        <v>815</v>
+        <v>873</v>
       </c>
     </row>
     <row r="11" ht="12.8">
@@ -5612,7 +5822,7 @@
         <v>22</v>
       </c>
       <c r="L11" t="s">
-        <v>816</v>
+        <v>874</v>
       </c>
     </row>
     <row r="12" ht="12.8">
@@ -5647,7 +5857,7 @@
         <v>28</v>
       </c>
       <c r="L16" t="s">
-        <v>817</v>
+        <v>875</v>
       </c>
     </row>
     <row r="17" ht="12.8">
@@ -5667,7 +5877,7 @@
         <v>31</v>
       </c>
       <c r="L17" t="s">
-        <v>818</v>
+        <v>876</v>
       </c>
     </row>
     <row r="18" ht="12.8">
@@ -5687,7 +5897,7 @@
         <v>33</v>
       </c>
       <c r="L18" t="s">
-        <v>819</v>
+        <v>877</v>
       </c>
     </row>
     <row r="19" ht="12.8">
@@ -5714,7 +5924,7 @@
         <v>35</v>
       </c>
       <c r="L22" t="s">
-        <v>820</v>
+        <v>878</v>
       </c>
     </row>
     <row r="23" ht="12.8">
@@ -5736,7 +5946,7 @@
         <v>37</v>
       </c>
       <c r="L25" t="s">
-        <v>821</v>
+        <v>879</v>
       </c>
     </row>
     <row r="26" ht="12.8">
@@ -5756,7 +5966,7 @@
         <v>40</v>
       </c>
       <c r="L26" t="s">
-        <v>822</v>
+        <v>880</v>
       </c>
     </row>
     <row r="27" ht="13.8">
@@ -5776,7 +5986,7 @@
         <v>43</v>
       </c>
       <c r="L27" t="s">
-        <v>823</v>
+        <v>881</v>
       </c>
     </row>
     <row r="28" ht="13.8">
@@ -5796,7 +6006,7 @@
         <v>46</v>
       </c>
       <c r="L28" t="s">
-        <v>824</v>
+        <v>882</v>
       </c>
     </row>
     <row r="29" ht="13.8">
@@ -5816,7 +6026,7 @@
         <v>49</v>
       </c>
       <c r="L29" t="s">
-        <v>825</v>
+        <v>883</v>
       </c>
     </row>
     <row r="30" ht="13.8">
@@ -5836,7 +6046,7 @@
         <v>52</v>
       </c>
       <c r="L30" t="s">
-        <v>826</v>
+        <v>884</v>
       </c>
     </row>
     <row r="31" ht="12.8">
@@ -5859,7 +6069,7 @@
         <v>56</v>
       </c>
       <c r="L31" t="s">
-        <v>827</v>
+        <v>885</v>
       </c>
     </row>
     <row r="32" ht="12.8">
@@ -5879,7 +6089,7 @@
         <v>33</v>
       </c>
       <c r="L32" t="s">
-        <v>819</v>
+        <v>877</v>
       </c>
     </row>
     <row r="33" ht="12.8">
@@ -5911,7 +6121,7 @@
         <v>58</v>
       </c>
       <c r="L36" t="s">
-        <v>828</v>
+        <v>886</v>
       </c>
     </row>
     <row r="37" ht="12.8">
@@ -5939,7 +6149,7 @@
         <v>60</v>
       </c>
       <c r="L40" t="s">
-        <v>829</v>
+        <v>887</v>
       </c>
     </row>
     <row r="41" ht="12.8">
@@ -5967,7 +6177,7 @@
         <v>62</v>
       </c>
       <c r="L44" t="s">
-        <v>830</v>
+        <v>888</v>
       </c>
     </row>
     <row r="45" ht="12.8">
@@ -5995,7 +6205,7 @@
         <v>64</v>
       </c>
       <c r="L48" t="s">
-        <v>831</v>
+        <v>889</v>
       </c>
     </row>
     <row r="49" ht="75.35">
@@ -6009,7 +6219,7 @@
         <v>66</v>
       </c>
       <c r="L49" t="s">
-        <v>832</v>
+        <v>890</v>
       </c>
     </row>
     <row r="50" ht="85.05">
@@ -6023,7 +6233,7 @@
         <v>68</v>
       </c>
       <c r="L50" t="s">
-        <v>833</v>
+        <v>891</v>
       </c>
     </row>
     <row r="51" ht="12.8">
@@ -6051,7 +6261,7 @@
         <v>70</v>
       </c>
       <c r="L54" t="s">
-        <v>834</v>
+        <v>892</v>
       </c>
     </row>
     <row r="55" ht="105.95">
@@ -6065,7 +6275,7 @@
         <v>72</v>
       </c>
       <c r="L55" t="s">
-        <v>835</v>
+        <v>893</v>
       </c>
     </row>
     <row r="56" ht="46.25">
@@ -6079,7 +6289,7 @@
         <v>74</v>
       </c>
       <c r="L56" t="s">
-        <v>836</v>
+        <v>894</v>
       </c>
     </row>
     <row r="57" ht="12.8">
@@ -6103,7 +6313,7 @@
         <v>76</v>
       </c>
       <c r="L60" t="s">
-        <v>837</v>
+        <v>895</v>
       </c>
     </row>
     <row r="61" ht="74.6">
@@ -6117,7 +6327,7 @@
         <v>78</v>
       </c>
       <c r="L61" t="s">
-        <v>838</v>
+        <v>896</v>
       </c>
     </row>
     <row r="62" ht="12.8">
@@ -6141,7 +6351,7 @@
         <v>81</v>
       </c>
       <c r="L65" t="s">
-        <v>839</v>
+        <v>897</v>
       </c>
     </row>
     <row r="66" ht="35.05">
@@ -6155,7 +6365,7 @@
         <v>83</v>
       </c>
       <c r="L66" t="s">
-        <v>840</v>
+        <v>898</v>
       </c>
     </row>
     <row r="67" ht="124.6">
@@ -6169,7 +6379,7 @@
         <v>85</v>
       </c>
       <c r="L67" t="s">
-        <v>841</v>
+        <v>899</v>
       </c>
     </row>
     <row r="68" ht="13.8">
@@ -6183,7 +6393,7 @@
         <v>87</v>
       </c>
       <c r="L68" t="s">
-        <v>842</v>
+        <v>900</v>
       </c>
     </row>
     <row r="69" ht="13.8">
@@ -6211,7 +6421,7 @@
         <v>91</v>
       </c>
       <c r="L70" t="s">
-        <v>843</v>
+        <v>901</v>
       </c>
     </row>
     <row r="71" ht="13.8">
@@ -6244,7 +6454,7 @@
         <v>97</v>
       </c>
       <c r="L74" t="s">
-        <v>844</v>
+        <v>902</v>
       </c>
     </row>
     <row r="75" ht="12.8">
@@ -6273,7 +6483,7 @@
         <v>102</v>
       </c>
       <c r="L80" t="s">
-        <v>845</v>
+        <v>903</v>
       </c>
     </row>
     <row r="84" ht="12.8">
@@ -6297,7 +6507,7 @@
         <v>105</v>
       </c>
       <c r="L89" t="s">
-        <v>846</v>
+        <v>904</v>
       </c>
     </row>
     <row r="90" ht="13.8">
@@ -6311,7 +6521,7 @@
         <v>107</v>
       </c>
       <c r="L90" t="s">
-        <v>847</v>
+        <v>905</v>
       </c>
     </row>
     <row r="91" ht="85.05">
@@ -6325,7 +6535,7 @@
         <v>109</v>
       </c>
       <c r="L91" t="s">
-        <v>848</v>
+        <v>906</v>
       </c>
     </row>
     <row r="92" ht="12.8">
@@ -6362,7 +6572,7 @@
         <v>113</v>
       </c>
       <c r="L97" t="s">
-        <v>849</v>
+        <v>907</v>
       </c>
     </row>
     <row r="98" ht="95.5">
@@ -6376,7 +6586,7 @@
         <v>115</v>
       </c>
       <c r="L98" t="s">
-        <v>850</v>
+        <v>908</v>
       </c>
     </row>
     <row r="99" ht="12.8">
@@ -6458,7 +6668,7 @@
         <v>122</v>
       </c>
       <c r="L108" t="s">
-        <v>851</v>
+        <v>909</v>
       </c>
     </row>
     <row r="109" ht="23.85">
@@ -6475,7 +6685,7 @@
         <v>124</v>
       </c>
       <c r="L109" t="s">
-        <v>852</v>
+        <v>910</v>
       </c>
     </row>
     <row r="110" ht="13.8">
@@ -6489,7 +6699,7 @@
         <v>126</v>
       </c>
       <c r="L110" t="s">
-        <v>853</v>
+        <v>911</v>
       </c>
     </row>
     <row r="111" ht="12.8">
@@ -6511,7 +6721,7 @@
         <v>129</v>
       </c>
       <c r="L112" t="s">
-        <v>854</v>
+        <v>912</v>
       </c>
     </row>
     <row r="113" ht="13.8">
@@ -6539,7 +6749,7 @@
         <v>131</v>
       </c>
       <c r="L114" t="s">
-        <v>855</v>
+        <v>913</v>
       </c>
     </row>
     <row r="115" ht="13.8">
@@ -6556,7 +6766,7 @@
         <v>133</v>
       </c>
       <c r="L115" t="s">
-        <v>856</v>
+        <v>914</v>
       </c>
     </row>
     <row r="116" ht="13.8">
@@ -6573,7 +6783,7 @@
         <v>135</v>
       </c>
       <c r="L116" t="s">
-        <v>857</v>
+        <v>915</v>
       </c>
     </row>
     <row r="117" ht="13.8">
@@ -6587,7 +6797,7 @@
         <v>137</v>
       </c>
       <c r="L117" t="s">
-        <v>858</v>
+        <v>916</v>
       </c>
     </row>
     <row r="118" ht="57.45">
@@ -6601,7 +6811,7 @@
         <v>139</v>
       </c>
       <c r="L118" t="s">
-        <v>859</v>
+        <v>917</v>
       </c>
     </row>
     <row r="119" ht="35.05">
@@ -6615,7 +6825,7 @@
         <v>141</v>
       </c>
       <c r="L119" t="s">
-        <v>860</v>
+        <v>918</v>
       </c>
     </row>
     <row r="120" ht="23.85">
@@ -6632,7 +6842,7 @@
         <v>143</v>
       </c>
       <c r="L120" t="s">
-        <v>861</v>
+        <v>919</v>
       </c>
     </row>
     <row r="121" ht="13.8">
@@ -6646,7 +6856,7 @@
         <v>145</v>
       </c>
       <c r="L121" t="s">
-        <v>862</v>
+        <v>920</v>
       </c>
     </row>
     <row r="122" ht="13.8">
@@ -6680,7 +6890,7 @@
         <v>147</v>
       </c>
       <c r="L123" t="s">
-        <v>863</v>
+        <v>921</v>
       </c>
     </row>
     <row r="124" ht="13.8">
@@ -6697,7 +6907,7 @@
         <v>149</v>
       </c>
       <c r="L124" t="s">
-        <v>864</v>
+        <v>922</v>
       </c>
     </row>
     <row r="125" ht="13.8">
@@ -6754,7 +6964,7 @@
         <v>156</v>
       </c>
       <c r="L134" t="s">
-        <v>865</v>
+        <v>923</v>
       </c>
     </row>
     <row r="135" ht="57.45">
@@ -6768,7 +6978,7 @@
         <v>158</v>
       </c>
       <c r="L135" t="s">
-        <v>866</v>
+        <v>924</v>
       </c>
     </row>
     <row r="136" ht="13.8">
@@ -6785,7 +6995,7 @@
         <v>160</v>
       </c>
       <c r="L136" t="s">
-        <v>867</v>
+        <v>925</v>
       </c>
     </row>
     <row r="137" ht="35.05">
@@ -6799,7 +7009,7 @@
         <v>162</v>
       </c>
       <c r="L137" t="s">
-        <v>868</v>
+        <v>926</v>
       </c>
     </row>
     <row r="138" ht="35.05">
@@ -6816,7 +7026,7 @@
         <v>164</v>
       </c>
       <c r="L138" t="s">
-        <v>869</v>
+        <v>927</v>
       </c>
     </row>
     <row r="139" ht="13.8">
@@ -6847,7 +7057,7 @@
         <v>166</v>
       </c>
       <c r="L140" t="s">
-        <v>870</v>
+        <v>928</v>
       </c>
     </row>
     <row r="141" ht="13.8">
@@ -6861,7 +7071,7 @@
         <v>168</v>
       </c>
       <c r="L141" t="s">
-        <v>871</v>
+        <v>929</v>
       </c>
     </row>
     <row r="142" ht="68.65">
@@ -6875,7 +7085,7 @@
         <v>170</v>
       </c>
       <c r="L142" t="s">
-        <v>872</v>
+        <v>930</v>
       </c>
     </row>
     <row r="143" ht="23.85">
@@ -6892,7 +7102,7 @@
         <v>172</v>
       </c>
       <c r="L143" t="s">
-        <v>873</v>
+        <v>931</v>
       </c>
     </row>
     <row r="144" ht="13.8">
@@ -6906,7 +7116,7 @@
         <v>137</v>
       </c>
       <c r="L144" t="s">
-        <v>858</v>
+        <v>916</v>
       </c>
     </row>
     <row r="145" ht="68.65">
@@ -6923,7 +7133,7 @@
         <v>174</v>
       </c>
       <c r="L145" t="s">
-        <v>874</v>
+        <v>932</v>
       </c>
     </row>
     <row r="146" ht="13.8">
@@ -6937,7 +7147,7 @@
         <v>176</v>
       </c>
       <c r="L146" t="s">
-        <v>875</v>
+        <v>933</v>
       </c>
     </row>
     <row r="147" ht="13.8">
@@ -6954,7 +7164,7 @@
         <v>178</v>
       </c>
       <c r="L147" t="s">
-        <v>876</v>
+        <v>934</v>
       </c>
     </row>
     <row r="148" ht="23.85">
@@ -6968,7 +7178,7 @@
         <v>180</v>
       </c>
       <c r="L148" t="s">
-        <v>877</v>
+        <v>935</v>
       </c>
     </row>
     <row r="149" ht="12.8">
@@ -7032,7 +7242,7 @@
         <v>186</v>
       </c>
       <c r="L158" t="s">
-        <v>878</v>
+        <v>936</v>
       </c>
     </row>
     <row r="159" ht="23.85">
@@ -7046,7 +7256,7 @@
         <v>188</v>
       </c>
       <c r="L159" t="s">
-        <v>879</v>
+        <v>937</v>
       </c>
     </row>
     <row r="160" ht="23.85">
@@ -7063,7 +7273,7 @@
         <v>190</v>
       </c>
       <c r="L160" t="s">
-        <v>880</v>
+        <v>938</v>
       </c>
     </row>
     <row r="161" ht="68.65">
@@ -7077,7 +7287,7 @@
         <v>192</v>
       </c>
       <c r="L161" t="s">
-        <v>881</v>
+        <v>939</v>
       </c>
     </row>
     <row r="162" ht="91">
@@ -7091,7 +7301,7 @@
         <v>194</v>
       </c>
       <c r="L162" t="s">
-        <v>882</v>
+        <v>940</v>
       </c>
     </row>
     <row r="163" ht="46.25">
@@ -7105,7 +7315,7 @@
         <v>196</v>
       </c>
       <c r="L163" t="s">
-        <v>883</v>
+        <v>941</v>
       </c>
     </row>
     <row r="164" ht="13.8">
@@ -7136,7 +7346,7 @@
         <v>199</v>
       </c>
       <c r="L165" t="s">
-        <v>884</v>
+        <v>942</v>
       </c>
     </row>
     <row r="166" ht="57.45">
@@ -7153,7 +7363,7 @@
         <v>201</v>
       </c>
       <c r="L166" t="s">
-        <v>885</v>
+        <v>943</v>
       </c>
     </row>
     <row r="167" ht="13.8">
@@ -7187,7 +7397,7 @@
         <v>203</v>
       </c>
       <c r="L168" t="s">
-        <v>886</v>
+        <v>944</v>
       </c>
     </row>
     <row r="169" ht="23.85">
@@ -7201,7 +7411,7 @@
         <v>205</v>
       </c>
       <c r="L169" t="s">
-        <v>887</v>
+        <v>945</v>
       </c>
     </row>
     <row r="170" ht="35.05">
@@ -7218,7 +7428,7 @@
         <v>207</v>
       </c>
       <c r="L170" t="s">
-        <v>888</v>
+        <v>946</v>
       </c>
     </row>
     <row r="171" ht="35.05">
@@ -7232,7 +7442,7 @@
         <v>209</v>
       </c>
       <c r="L171" t="s">
-        <v>889</v>
+        <v>947</v>
       </c>
     </row>
     <row r="172" ht="56.7">
@@ -7246,7 +7456,7 @@
         <v>211</v>
       </c>
       <c r="L172" t="s">
-        <v>890</v>
+        <v>948</v>
       </c>
     </row>
     <row r="173" ht="13.8">
@@ -7307,7 +7517,7 @@
         <v>215</v>
       </c>
       <c r="L182" t="s">
-        <v>891</v>
+        <v>949</v>
       </c>
     </row>
     <row r="183" ht="13.8">
@@ -7324,7 +7534,7 @@
         <v>217</v>
       </c>
       <c r="L183" t="s">
-        <v>892</v>
+        <v>950</v>
       </c>
     </row>
     <row r="184" ht="24.6">
@@ -7338,7 +7548,7 @@
         <v>219</v>
       </c>
       <c r="L184" t="s">
-        <v>893</v>
+        <v>951</v>
       </c>
     </row>
     <row r="185" ht="13.8">
@@ -7386,7 +7596,7 @@
         <v>221</v>
       </c>
       <c r="L187" t="s">
-        <v>894</v>
+        <v>952</v>
       </c>
     </row>
     <row r="188" ht="35.05">
@@ -7400,7 +7610,7 @@
         <v>223</v>
       </c>
       <c r="L188" t="s">
-        <v>895</v>
+        <v>953</v>
       </c>
     </row>
     <row r="189" ht="13.8">
@@ -7448,7 +7658,7 @@
         <v>225</v>
       </c>
       <c r="L191" t="s">
-        <v>896</v>
+        <v>954</v>
       </c>
     </row>
     <row r="192" ht="35.05">
@@ -7462,7 +7672,7 @@
         <v>227</v>
       </c>
       <c r="L192" t="s">
-        <v>897</v>
+        <v>955</v>
       </c>
     </row>
     <row r="193" ht="13.8">
@@ -7507,7 +7717,7 @@
         <v>229</v>
       </c>
       <c r="L195" t="s">
-        <v>898</v>
+        <v>956</v>
       </c>
     </row>
     <row r="196" ht="13.8">
@@ -7524,7 +7734,7 @@
         <v>231</v>
       </c>
       <c r="L196" t="s">
-        <v>899</v>
+        <v>957</v>
       </c>
     </row>
     <row r="197" ht="23.85">
@@ -7538,7 +7748,7 @@
         <v>233</v>
       </c>
       <c r="L197" t="s">
-        <v>900</v>
+        <v>958</v>
       </c>
     </row>
     <row r="198" ht="13.8">
@@ -7566,7 +7776,7 @@
         <v>235</v>
       </c>
       <c r="L199" t="s">
-        <v>901</v>
+        <v>959</v>
       </c>
     </row>
     <row r="200" ht="13.8">
@@ -7597,7 +7807,7 @@
         <v>237</v>
       </c>
       <c r="L201" t="s">
-        <v>902</v>
+        <v>960</v>
       </c>
     </row>
     <row r="202" ht="13.8">
@@ -7614,7 +7824,7 @@
         <v>239</v>
       </c>
       <c r="L202" t="s">
-        <v>903</v>
+        <v>961</v>
       </c>
     </row>
     <row r="203" ht="13.8">
@@ -7628,7 +7838,7 @@
         <v>241</v>
       </c>
       <c r="L203" t="s">
-        <v>904</v>
+        <v>962</v>
       </c>
     </row>
     <row r="204" ht="13.8">
@@ -7656,7 +7866,7 @@
         <v>243</v>
       </c>
       <c r="L205" t="s">
-        <v>905</v>
+        <v>963</v>
       </c>
     </row>
     <row r="206" ht="13.8">
@@ -7718,7 +7928,7 @@
         <v>246</v>
       </c>
       <c r="L216" t="s">
-        <v>906</v>
+        <v>964</v>
       </c>
     </row>
     <row r="217" ht="13.8">
@@ -7735,7 +7945,7 @@
         <v>248</v>
       </c>
       <c r="L217" t="s">
-        <v>907</v>
+        <v>965</v>
       </c>
     </row>
     <row r="218" ht="68.65">
@@ -7749,7 +7959,7 @@
         <v>250</v>
       </c>
       <c r="L218" t="s">
-        <v>908</v>
+        <v>966</v>
       </c>
     </row>
     <row r="219" ht="64.15">
@@ -7766,7 +7976,7 @@
         <v>252</v>
       </c>
       <c r="L219" t="s">
-        <v>909</v>
+        <v>967</v>
       </c>
     </row>
     <row r="220" ht="13.8">
@@ -7780,7 +7990,7 @@
         <v>254</v>
       </c>
       <c r="L220" t="s">
-        <v>910</v>
+        <v>968</v>
       </c>
     </row>
     <row r="221" ht="13.8">
@@ -7814,7 +8024,7 @@
         <v>256</v>
       </c>
       <c r="L222" t="s">
-        <v>911</v>
+        <v>969</v>
       </c>
     </row>
     <row r="223" ht="13.8">
@@ -7842,7 +8052,7 @@
         <v>258</v>
       </c>
       <c r="L224" t="s">
-        <v>912</v>
+        <v>970</v>
       </c>
     </row>
     <row r="225" ht="46.25">
@@ -7859,7 +8069,7 @@
         <v>260</v>
       </c>
       <c r="L225" t="s">
-        <v>913</v>
+        <v>971</v>
       </c>
     </row>
     <row r="226" ht="13.8">
@@ -7876,7 +8086,7 @@
         <v>262</v>
       </c>
       <c r="L226" t="s">
-        <v>914</v>
+        <v>972</v>
       </c>
     </row>
     <row r="227" ht="13.8">
@@ -7890,7 +8100,7 @@
         <v>264</v>
       </c>
       <c r="L227" t="s">
-        <v>915</v>
+        <v>973</v>
       </c>
     </row>
     <row r="228" ht="13.4">
@@ -7904,7 +8114,7 @@
         <v>266</v>
       </c>
       <c r="L228" t="s">
-        <v>916</v>
+        <v>974</v>
       </c>
     </row>
     <row r="229" ht="35.05">
@@ -7918,7 +8128,7 @@
         <v>268</v>
       </c>
       <c r="L229" t="s">
-        <v>917</v>
+        <v>975</v>
       </c>
     </row>
     <row r="230" ht="13.8">
@@ -7956,7 +8166,7 @@
         <v>272</v>
       </c>
       <c r="L239" t="s">
-        <v>918</v>
+        <v>976</v>
       </c>
     </row>
     <row r="240" ht="57.45">
@@ -7970,7 +8180,7 @@
         <v>274</v>
       </c>
       <c r="L240" t="s">
-        <v>919</v>
+        <v>977</v>
       </c>
     </row>
     <row r="241" ht="12.8">
@@ -8000,7 +8210,7 @@
         <v>277</v>
       </c>
       <c r="L244" t="s">
-        <v>920</v>
+        <v>978</v>
       </c>
     </row>
     <row r="245" ht="64.15">
@@ -8014,7 +8224,7 @@
         <v>279</v>
       </c>
       <c r="L245" t="s">
-        <v>921</v>
+        <v>979</v>
       </c>
     </row>
     <row r="246" ht="13.8">
@@ -8043,7 +8253,7 @@
         <v>281</v>
       </c>
       <c r="L247" t="s">
-        <v>922</v>
+        <v>980</v>
       </c>
     </row>
     <row r="248" ht="13.8">
@@ -8074,7 +8284,7 @@
         <v>283</v>
       </c>
       <c r="L249" t="s">
-        <v>923</v>
+        <v>981</v>
       </c>
     </row>
     <row r="250" ht="35.05">
@@ -8088,7 +8298,7 @@
         <v>285</v>
       </c>
       <c r="L250" t="s">
-        <v>924</v>
+        <v>982</v>
       </c>
     </row>
     <row r="251" ht="91">
@@ -8102,7 +8312,7 @@
         <v>287</v>
       </c>
       <c r="L251" t="s">
-        <v>925</v>
+        <v>983</v>
       </c>
     </row>
     <row r="252" ht="64.15">
@@ -8116,7 +8326,7 @@
         <v>289</v>
       </c>
       <c r="L252" t="s">
-        <v>926</v>
+        <v>984</v>
       </c>
     </row>
     <row r="253" ht="13.8">
@@ -8150,7 +8360,7 @@
         <v>292</v>
       </c>
       <c r="L257" t="s">
-        <v>927</v>
+        <v>985</v>
       </c>
     </row>
     <row r="258" ht="64.15">
@@ -8164,7 +8374,7 @@
         <v>294</v>
       </c>
       <c r="L258" t="s">
-        <v>928</v>
+        <v>986</v>
       </c>
     </row>
     <row r="259" ht="13.8">
@@ -8187,7 +8397,7 @@
         <v>297</v>
       </c>
       <c r="L260" t="s">
-        <v>929</v>
+        <v>987</v>
       </c>
     </row>
     <row r="261" ht="12.8">
@@ -8222,7 +8432,7 @@
         <v>300</v>
       </c>
       <c r="L266" t="s">
-        <v>930</v>
+        <v>988</v>
       </c>
     </row>
     <row r="267" ht="23.85">
@@ -8236,7 +8446,7 @@
         <v>302</v>
       </c>
       <c r="L267" t="s">
-        <v>931</v>
+        <v>989</v>
       </c>
     </row>
     <row r="268" ht="35.05">
@@ -8250,7 +8460,7 @@
         <v>304</v>
       </c>
       <c r="L268" t="s">
-        <v>932</v>
+        <v>990</v>
       </c>
     </row>
     <row r="269" ht="35.05">
@@ -8264,7 +8474,7 @@
         <v>306</v>
       </c>
       <c r="L269" t="s">
-        <v>933</v>
+        <v>991</v>
       </c>
     </row>
     <row r="270" ht="68.65">
@@ -8278,7 +8488,7 @@
         <v>308</v>
       </c>
       <c r="L270" t="s">
-        <v>934</v>
+        <v>992</v>
       </c>
     </row>
     <row r="271" ht="12.8">
@@ -8332,7 +8542,7 @@
         <v>313</v>
       </c>
       <c r="L279" s="4" t="s">
-        <v>935</v>
+        <v>993</v>
       </c>
     </row>
     <row r="280" ht="12.8">
@@ -8349,7 +8559,7 @@
         <v>315</v>
       </c>
       <c r="L280" t="s">
-        <v>936</v>
+        <v>994</v>
       </c>
     </row>
     <row r="281" ht="12.8">
@@ -8363,7 +8573,7 @@
         <v>317</v>
       </c>
       <c r="L281" t="s">
-        <v>937</v>
+        <v>995</v>
       </c>
     </row>
     <row r="282" ht="12.8">
@@ -8394,7 +8604,7 @@
         <v>319</v>
       </c>
       <c r="L283" t="s">
-        <v>938</v>
+        <v>996</v>
       </c>
     </row>
     <row r="284" ht="43.25">
@@ -8408,7 +8618,7 @@
         <v>321</v>
       </c>
       <c r="L284" t="s">
-        <v>939</v>
+        <v>997</v>
       </c>
     </row>
     <row r="285" ht="68.65">
@@ -8422,7 +8632,7 @@
         <v>323</v>
       </c>
       <c r="L285" t="s">
-        <v>940</v>
+        <v>998</v>
       </c>
     </row>
     <row r="286" ht="23.85">
@@ -8436,7 +8646,7 @@
         <v>325</v>
       </c>
       <c r="L286" t="s">
-        <v>941</v>
+        <v>999</v>
       </c>
     </row>
     <row r="287" ht="12.8">
@@ -8473,7 +8683,7 @@
         <v>331</v>
       </c>
       <c r="L294" t="s">
-        <v>942</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="295" ht="12.8">
@@ -8504,7 +8714,7 @@
         <v>333</v>
       </c>
       <c r="L296" t="s">
-        <v>943</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="297" ht="95.5">
@@ -8521,7 +8731,7 @@
         <v>335</v>
       </c>
       <c r="L297" t="s">
-        <v>944</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="298" ht="13.8">
@@ -8552,7 +8762,7 @@
         <v>337</v>
       </c>
       <c r="L299" t="s">
-        <v>945</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="300" ht="85.8">
@@ -8569,7 +8779,7 @@
         <v>339</v>
       </c>
       <c r="L300" t="s">
-        <v>946</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="301" ht="13.8">
@@ -8583,7 +8793,7 @@
         <v>341</v>
       </c>
       <c r="L301" t="s">
-        <v>947</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="302" ht="13.8">
@@ -8628,7 +8838,7 @@
         <v>343</v>
       </c>
       <c r="L304" t="s">
-        <v>948</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="305" ht="13.8">
@@ -8645,7 +8855,7 @@
         <v>345</v>
       </c>
       <c r="L305" t="s">
-        <v>949</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="306" ht="46.25">
@@ -8659,7 +8869,7 @@
         <v>347</v>
       </c>
       <c r="L306" t="s">
-        <v>950</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="307" ht="13.8">
@@ -8676,7 +8886,7 @@
         <v>349</v>
       </c>
       <c r="L307" t="s">
-        <v>951</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="308" ht="35.05">
@@ -8690,7 +8900,7 @@
         <v>351</v>
       </c>
       <c r="L308" t="s">
-        <v>952</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="309" ht="13.8">
@@ -8707,7 +8917,7 @@
         <v>353</v>
       </c>
       <c r="L309" t="s">
-        <v>953</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="310" ht="13.8">
@@ -8735,7 +8945,7 @@
         <v>355</v>
       </c>
       <c r="L311" t="s">
-        <v>954</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="312" ht="64.15">
@@ -8749,7 +8959,7 @@
         <v>357</v>
       </c>
       <c r="L312" t="s">
-        <v>955</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="313" ht="13.8">
@@ -8776,7 +8986,7 @@
         <v>360</v>
       </c>
       <c r="L318" t="s">
-        <v>956</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="319" ht="116.4">
@@ -8790,7 +9000,7 @@
         <v>362</v>
       </c>
       <c r="L319" t="s">
-        <v>957</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="320" ht="13.8">
@@ -8814,7 +9024,7 @@
         <v>366</v>
       </c>
       <c r="L321" t="s">
-        <v>958</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="322" ht="57.45">
@@ -8828,7 +9038,7 @@
         <v>368</v>
       </c>
       <c r="L322" t="s">
-        <v>959</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="323" ht="13.8">
@@ -8867,7 +9077,7 @@
         <v>371</v>
       </c>
       <c r="L330" t="s">
-        <v>960</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="331" ht="23.85">
@@ -8881,7 +9091,7 @@
         <v>373</v>
       </c>
       <c r="L331" t="s">
-        <v>961</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="332" ht="79.85">
@@ -8898,7 +9108,7 @@
         <v>375</v>
       </c>
       <c r="L332" t="s">
-        <v>962</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="333" ht="57.45">
@@ -8912,7 +9122,7 @@
         <v>377</v>
       </c>
       <c r="L333" t="s">
-        <v>963</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="334" ht="12.8">
@@ -8937,7 +9147,7 @@
         <v>379</v>
       </c>
       <c r="L336" t="s">
-        <v>964</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="338" ht="12.8">
@@ -8982,7 +9192,7 @@
         <v>385</v>
       </c>
       <c r="L344" s="4" t="s">
-        <v>965</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="345" s="1" customFormat="1" ht="12.8">
@@ -9075,7 +9285,7 @@
         <v>387</v>
       </c>
       <c r="L350" s="4" t="s">
-        <v>966</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="351" s="1" customFormat="1" ht="13.8">
@@ -9099,7 +9309,7 @@
         <v>389</v>
       </c>
       <c r="L351" s="4" t="s">
-        <v>967</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="352" s="1" customFormat="1" ht="57.45">
@@ -9123,7 +9333,7 @@
         <v>391</v>
       </c>
       <c r="L352" s="4" t="s">
-        <v>968</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="353" s="1" customFormat="1" ht="12.8">
@@ -9147,7 +9357,7 @@
         <v>393</v>
       </c>
       <c r="L353" s="4" t="s">
-        <v>969</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="354" s="1" customFormat="1" ht="35.05">
@@ -9171,7 +9381,7 @@
         <v>395</v>
       </c>
       <c r="L354" s="4" t="s">
-        <v>970</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="355" s="1" customFormat="1" ht="13.8">
@@ -9219,7 +9429,7 @@
         <v>397</v>
       </c>
       <c r="L356" s="4" t="s">
-        <v>971</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="357" s="1" customFormat="1" ht="13.8">
@@ -9243,7 +9453,7 @@
         <v>399</v>
       </c>
       <c r="L357" s="4" t="s">
-        <v>972</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="358" s="1" customFormat="1" ht="22.35">
@@ -9291,7 +9501,7 @@
         <v>401</v>
       </c>
       <c r="L359" s="4" t="s">
-        <v>973</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="360" s="1" customFormat="1" ht="23.85">
@@ -9315,7 +9525,7 @@
         <v>403</v>
       </c>
       <c r="L360" s="4" t="s">
-        <v>974</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="361" s="1" customFormat="1" ht="23.85">
@@ -9339,7 +9549,7 @@
         <v>405</v>
       </c>
       <c r="L361" s="4" t="s">
-        <v>975</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="362" s="1" customFormat="1" ht="13.8">
@@ -9431,7 +9641,7 @@
         <v>410</v>
       </c>
       <c r="L366" s="4" t="s">
-        <v>976</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="367" s="1" customFormat="1" ht="13.8">
@@ -9503,7 +9713,7 @@
         <v>412</v>
       </c>
       <c r="L369" s="4" t="s">
-        <v>977</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="370" s="1" customFormat="1" ht="12.8">
@@ -9527,7 +9737,7 @@
         <v>414</v>
       </c>
       <c r="L370" s="4" t="s">
-        <v>978</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="371" s="1" customFormat="1" ht="12.8">
@@ -9551,7 +9761,7 @@
         <v>416</v>
       </c>
       <c r="L371" s="4" t="s">
-        <v>979</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="372" s="1" customFormat="1" ht="23.85">
@@ -9575,7 +9785,7 @@
         <v>418</v>
       </c>
       <c r="L372" s="4" t="s">
-        <v>980</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="373" s="1" customFormat="1" ht="23.85">
@@ -9599,7 +9809,7 @@
         <v>420</v>
       </c>
       <c r="L373" s="4" t="s">
-        <v>981</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="374" s="1" customFormat="1" ht="12.8">
@@ -9640,7 +9850,7 @@
         <v>422</v>
       </c>
       <c r="L375" s="4" t="s">
-        <v>982</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="376" s="1" customFormat="1" ht="12.8">
@@ -9689,7 +9899,7 @@
         <v>424</v>
       </c>
       <c r="L378" s="4" t="s">
-        <v>983</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="379" s="1" customFormat="1" ht="12.8">
@@ -9713,7 +9923,7 @@
         <v>426</v>
       </c>
       <c r="L379" s="4" t="s">
-        <v>984</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="380" s="1" customFormat="1" ht="12.8">
@@ -9761,7 +9971,7 @@
         <v>428</v>
       </c>
       <c r="L381" s="4" t="s">
-        <v>985</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="382" s="1" customFormat="1" ht="23.85">
@@ -9785,7 +9995,7 @@
         <v>430</v>
       </c>
       <c r="L382" s="4" t="s">
-        <v>986</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="383" s="1" customFormat="1" ht="12.8">
@@ -9809,7 +10019,7 @@
         <v>432</v>
       </c>
       <c r="L383" s="4" t="s">
-        <v>987</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="384" s="1" customFormat="1" ht="35.05">
@@ -9833,7 +10043,7 @@
         <v>434</v>
       </c>
       <c r="L384" s="4" t="s">
-        <v>988</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="385" s="1" customFormat="1" ht="13.8">
@@ -9857,7 +10067,7 @@
         <v>436</v>
       </c>
       <c r="L385" s="4" t="s">
-        <v>989</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="386" s="1" customFormat="1" ht="13.8">
@@ -9881,7 +10091,7 @@
         <v>438</v>
       </c>
       <c r="L386" s="4" t="s">
-        <v>990</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="387" s="1" customFormat="1" ht="13.8">
@@ -9905,7 +10115,7 @@
         <v>440</v>
       </c>
       <c r="L387" s="4" t="s">
-        <v>991</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="388" s="1" customFormat="1" ht="13.8">
@@ -9929,7 +10139,7 @@
         <v>442</v>
       </c>
       <c r="L388" s="4" t="s">
-        <v>992</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="389" s="1" customFormat="1" ht="13.8">
@@ -9953,7 +10163,7 @@
         <v>444</v>
       </c>
       <c r="L389" s="4" t="s">
-        <v>993</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="390" s="1" customFormat="1" ht="13.8">
@@ -9977,7 +10187,7 @@
         <v>446</v>
       </c>
       <c r="L390" s="4" t="s">
-        <v>994</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="391" s="1" customFormat="1" ht="13.8">
@@ -10001,7 +10211,7 @@
         <v>448</v>
       </c>
       <c r="L391" s="4" t="s">
-        <v>995</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="392" s="1" customFormat="1" ht="23.85">
@@ -10025,7 +10235,7 @@
         <v>450</v>
       </c>
       <c r="L392" s="4" t="s">
-        <v>996</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="393" s="1" customFormat="1" ht="13.8">
@@ -10049,7 +10259,7 @@
         <v>452</v>
       </c>
       <c r="L393" s="4" t="s">
-        <v>997</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="394" s="1" customFormat="1" ht="13.8">
@@ -10086,7 +10296,7 @@
         <v>454</v>
       </c>
       <c r="L395" s="4" t="s">
-        <v>998</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="396" s="1" customFormat="1" ht="13.8">
@@ -10110,7 +10320,7 @@
         <v>456</v>
       </c>
       <c r="L396" s="4" t="s">
-        <v>999</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="397" s="1" customFormat="1" ht="13.8">
@@ -10147,7 +10357,7 @@
         <v>458</v>
       </c>
       <c r="L398" s="4" t="s">
-        <v>998</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="399" s="1" customFormat="1" ht="13.8">
@@ -10171,7 +10381,7 @@
         <v>460</v>
       </c>
       <c r="L399" s="4" t="s">
-        <v>1000</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="400" s="1" customFormat="1" ht="13.8">
@@ -10232,7 +10442,7 @@
         <v>462</v>
       </c>
       <c r="L402" s="4" t="s">
-        <v>1001</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="403" s="1" customFormat="1" ht="13.8">
@@ -10280,7 +10490,7 @@
         <v>464</v>
       </c>
       <c r="L404" s="4" t="s">
-        <v>1002</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="405" s="1" customFormat="1" ht="13.8">
@@ -10304,7 +10514,7 @@
         <v>466</v>
       </c>
       <c r="L405" s="4" t="s">
-        <v>1003</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="406" s="1" customFormat="1" ht="23.85">
@@ -10328,7 +10538,7 @@
         <v>468</v>
       </c>
       <c r="L406" s="4" t="s">
-        <v>1004</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="407" s="1" customFormat="1" ht="23.85">
@@ -10352,7 +10562,7 @@
         <v>470</v>
       </c>
       <c r="L407" s="4" t="s">
-        <v>1005</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="408" s="1" customFormat="1" ht="35.05">
@@ -10376,7 +10586,7 @@
         <v>472</v>
       </c>
       <c r="L408" s="4" t="s">
-        <v>1006</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="409" s="1" customFormat="1" ht="13.8">
@@ -10400,7 +10610,7 @@
         <v>474</v>
       </c>
       <c r="L409" s="4" t="s">
-        <v>1007</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="410" s="1" customFormat="1" ht="13.8">
@@ -10424,7 +10634,7 @@
         <v>476</v>
       </c>
       <c r="L410" s="4" t="s">
-        <v>1008</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="411" s="1" customFormat="1" ht="13.8">
@@ -10472,7 +10682,7 @@
         <v>478</v>
       </c>
       <c r="L412" s="4" t="s">
-        <v>1009</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="413" s="1" customFormat="1" ht="23.85">
@@ -10496,7 +10706,7 @@
         <v>480</v>
       </c>
       <c r="L413" s="4" t="s">
-        <v>1010</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="414" s="1" customFormat="1" ht="13.8">
@@ -10520,7 +10730,7 @@
         <v>482</v>
       </c>
       <c r="L414" s="4" t="s">
-        <v>1011</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="415" s="1" customFormat="1" ht="57.45">
@@ -10544,7 +10754,7 @@
         <v>484</v>
       </c>
       <c r="L415" s="4" t="s">
-        <v>1012</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="416" s="1" customFormat="1" ht="13.8">
@@ -10568,7 +10778,7 @@
         <v>486</v>
       </c>
       <c r="L416" s="4" t="s">
-        <v>1013</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="417" s="1" customFormat="1" ht="13.8">
@@ -10592,7 +10802,7 @@
         <v>458</v>
       </c>
       <c r="L417" s="4" t="s">
-        <v>998</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="418" s="1" customFormat="1" ht="13.8">
@@ -10640,7 +10850,7 @@
         <v>488</v>
       </c>
       <c r="L419" s="4" t="s">
-        <v>1014</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="420" s="1" customFormat="1" ht="13.8">
@@ -10688,7 +10898,7 @@
         <v>490</v>
       </c>
       <c r="L421" s="4" t="s">
-        <v>1015</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="422" s="1" customFormat="1" ht="13.8">
@@ -10712,7 +10922,7 @@
         <v>492</v>
       </c>
       <c r="L422" s="4" t="s">
-        <v>1016</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="423" s="1" customFormat="1" ht="12.8">
@@ -10792,7 +11002,7 @@
         <v>496</v>
       </c>
       <c r="L430" s="4" t="s">
-        <v>1017</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="431" s="1" customFormat="1" ht="13.8">
@@ -10816,7 +11026,7 @@
         <v>498</v>
       </c>
       <c r="L431" s="4" t="s">
-        <v>1018</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="432" s="1" customFormat="1" ht="25.35">
@@ -10838,7 +11048,7 @@
         <v>500</v>
       </c>
       <c r="L432" s="4" t="s">
-        <v>1019</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="433" s="1" customFormat="1" ht="102.2">
@@ -10862,7 +11072,7 @@
         <v>502</v>
       </c>
       <c r="L433" s="4" t="s">
-        <v>1020</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="434" s="1" customFormat="1" ht="13.8">
@@ -10886,7 +11096,7 @@
         <v>504</v>
       </c>
       <c r="L434" s="4" t="s">
-        <v>1021</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="435" s="1" customFormat="1" ht="13.8">
@@ -10910,7 +11120,7 @@
         <v>505</v>
       </c>
       <c r="L435" s="4" t="s">
-        <v>998</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="436" s="1" customFormat="1" ht="23.85">
@@ -10934,7 +11144,7 @@
         <v>507</v>
       </c>
       <c r="L436" s="4" t="s">
-        <v>1022</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="437" s="1" customFormat="1" ht="57.45">
@@ -10958,7 +11168,7 @@
         <v>509</v>
       </c>
       <c r="L437" s="4" t="s">
-        <v>1023</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="438" s="1" customFormat="1" ht="46.25">
@@ -10980,7 +11190,7 @@
         <v>511</v>
       </c>
       <c r="L438" s="4" t="s">
-        <v>1024</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="439" s="1" customFormat="1" ht="13.8">
@@ -11004,7 +11214,7 @@
         <v>513</v>
       </c>
       <c r="L439" s="4" t="s">
-        <v>1025</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="440" s="1" customFormat="1" ht="23.85">
@@ -11026,7 +11236,7 @@
         <v>515</v>
       </c>
       <c r="L440" s="4" t="s">
-        <v>1026</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="441" ht="12.8">
@@ -11063,7 +11273,7 @@
         <v>215</v>
       </c>
       <c r="L446" t="s">
-        <v>1027</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="447" ht="23.85">
@@ -11078,7 +11288,7 @@
         <v>217</v>
       </c>
       <c r="L447" t="s">
-        <v>1028</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="448" ht="13.8">
@@ -11091,7 +11301,7 @@
       </c>
       <c r="K448" s="14"/>
       <c r="L448" t="s">
-        <v>1029</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="449" ht="35.05">
@@ -11104,7 +11314,7 @@
       </c>
       <c r="K449" s="14"/>
       <c r="L449" t="s">
-        <v>1030</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="450" ht="13.8">
@@ -11117,7 +11327,7 @@
       </c>
       <c r="K450" s="14"/>
       <c r="L450" t="s">
-        <v>1031</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="451" ht="12.8">
@@ -11154,7 +11364,7 @@
         <v>525</v>
       </c>
       <c r="L460" t="s">
-        <v>1032</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="461" ht="46.25">
@@ -11168,7 +11378,7 @@
         <v>527</v>
       </c>
       <c r="L461" t="s">
-        <v>1033</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="462" ht="23.85">
@@ -11185,7 +11395,7 @@
         <v>529</v>
       </c>
       <c r="L462" t="s">
-        <v>1034</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="463" ht="35.05">
@@ -11199,7 +11409,7 @@
         <v>531</v>
       </c>
       <c r="L463" t="s">
-        <v>1035</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="464" ht="35.05">
@@ -11213,7 +11423,7 @@
         <v>533</v>
       </c>
       <c r="L464" t="s">
-        <v>1036</v>
+        <v>1094</v>
       </c>
       <c r="M464" s="1"/>
       <c r="N464" s="1"/>
@@ -11232,7 +11442,7 @@
         <v>535</v>
       </c>
       <c r="L465" t="s">
-        <v>1037</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="466" ht="37.3">
@@ -11246,7 +11456,7 @@
         <v>537</v>
       </c>
       <c r="L466" t="s">
-        <v>1038</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="467" ht="13.8">
@@ -11260,7 +11470,7 @@
         <v>539</v>
       </c>
       <c r="L467" t="s">
-        <v>1039</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="468" ht="13.8">
@@ -11274,7 +11484,7 @@
         <v>541</v>
       </c>
       <c r="L468" t="s">
-        <v>1040</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="469" ht="13.8">
@@ -11318,7 +11528,7 @@
         <v>543</v>
       </c>
       <c r="L471" t="s">
-        <v>1041</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="472" ht="35.05">
@@ -11335,7 +11545,7 @@
         <v>545</v>
       </c>
       <c r="L472" t="s">
-        <v>1042</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="473" ht="13.8">
@@ -11349,7 +11559,7 @@
         <v>547</v>
       </c>
       <c r="L473" t="s">
-        <v>1043</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="474" ht="13.8">
@@ -11376,7 +11586,7 @@
         <v>549</v>
       </c>
       <c r="L475" t="s">
-        <v>1044</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="476" ht="13.8">
@@ -11393,7 +11603,7 @@
         <v>551</v>
       </c>
       <c r="L476" t="s">
-        <v>1045</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="477" ht="79.85">
@@ -11410,7 +11620,7 @@
         <v>553</v>
       </c>
       <c r="L477" t="s">
-        <v>1046</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="478" ht="102.2">
@@ -11427,7 +11637,7 @@
         <v>555</v>
       </c>
       <c r="L478" t="s">
-        <v>1047</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="479" ht="13.8">
@@ -11458,7 +11668,7 @@
         <v>557</v>
       </c>
       <c r="L480" t="s">
-        <v>1048</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="481" ht="23.85">
@@ -11475,7 +11685,7 @@
         <v>559</v>
       </c>
       <c r="L481" t="s">
-        <v>1049</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="482" ht="23.85">
@@ -11492,7 +11702,7 @@
         <v>561</v>
       </c>
       <c r="L482" t="s">
-        <v>1050</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="483" ht="13.8">
@@ -11509,7 +11719,7 @@
         <v>513</v>
       </c>
       <c r="L483" t="s">
-        <v>1025</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="484" ht="13.8">
@@ -11523,7 +11733,7 @@
         <v>564</v>
       </c>
       <c r="L484" t="s">
-        <v>1051</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="485" ht="13.8">
@@ -11551,7 +11761,7 @@
         <v>566</v>
       </c>
       <c r="L486" t="s">
-        <v>1052</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="487" ht="46.25">
@@ -11565,7 +11775,7 @@
         <v>568</v>
       </c>
       <c r="L487" t="s">
-        <v>1053</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="488" ht="35.05">
@@ -11579,7 +11789,7 @@
         <v>570</v>
       </c>
       <c r="L488" t="s">
-        <v>1054</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="489" ht="35.05">
@@ -11593,7 +11803,7 @@
         <v>572</v>
       </c>
       <c r="L489" t="s">
-        <v>1055</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="490" ht="46.25">
@@ -11607,7 +11817,7 @@
         <v>574</v>
       </c>
       <c r="L490" t="s">
-        <v>1056</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="491" ht="13.8">
@@ -11643,7 +11853,7 @@
         <v>578</v>
       </c>
       <c r="L498" t="s">
-        <v>1057</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="499" ht="79.85">
@@ -11657,7 +11867,7 @@
         <v>580</v>
       </c>
       <c r="L499" t="s">
-        <v>1058</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="500" ht="12.8">
@@ -11689,7 +11899,7 @@
         <v>584</v>
       </c>
       <c r="L506" t="s">
-        <v>1059</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="507" ht="13.8">
@@ -11717,7 +11927,7 @@
         <v>586</v>
       </c>
       <c r="L508" t="s">
-        <v>1060</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="509" ht="13.8">
@@ -11750,7 +11960,7 @@
         <v>589</v>
       </c>
       <c r="L513" t="s">
-        <v>1061</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="514" ht="13.8">
@@ -11778,7 +11988,7 @@
         <v>591</v>
       </c>
       <c r="L515" t="s">
-        <v>1062</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="516" ht="13.8">
@@ -11811,7 +12021,7 @@
         <v>594</v>
       </c>
       <c r="L520" t="s">
-        <v>1063</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="521" ht="79.85">
@@ -11825,7 +12035,7 @@
         <v>596</v>
       </c>
       <c r="L521" t="s">
-        <v>1064</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="522" ht="13.8">
@@ -11866,7 +12076,7 @@
         <v>599</v>
       </c>
       <c r="L527" t="s">
-        <v>1065</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="528" ht="13.8">
@@ -11884,7 +12094,7 @@
         <v>601</v>
       </c>
       <c r="L529" t="s">
-        <v>1066</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="530" ht="13.8">
@@ -11911,7 +12121,7 @@
         <v>603</v>
       </c>
       <c r="L532" t="s">
-        <v>1067</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="533" ht="43.25">
@@ -11925,7 +12135,7 @@
         <v>605</v>
       </c>
       <c r="L533" t="s">
-        <v>1068</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="534" ht="57.45">
@@ -11939,7 +12149,7 @@
         <v>607</v>
       </c>
       <c r="L534" t="s">
-        <v>1069</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="535" ht="13.8">
@@ -11972,7 +12182,7 @@
         <v>610</v>
       </c>
       <c r="L539" t="s">
-        <v>1070</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="540" ht="79.85">
@@ -11986,7 +12196,7 @@
         <v>612</v>
       </c>
       <c r="L540" t="s">
-        <v>1071</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="541" ht="46.25">
@@ -12000,7 +12210,7 @@
         <v>614</v>
       </c>
       <c r="L541" t="s">
-        <v>1072</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="542" ht="13.8">
@@ -12033,7 +12243,7 @@
         <v>617</v>
       </c>
       <c r="L546" t="s">
-        <v>1073</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="547" ht="12.8">
@@ -12051,7 +12261,7 @@
         <v>619</v>
       </c>
       <c r="L547" t="s">
-        <v>1074</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="548" ht="12.8">
@@ -12118,7 +12328,7 @@
         <v>625</v>
       </c>
       <c r="L553" t="s">
-        <v>1075</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="554" ht="13.8">
@@ -12139,7 +12349,7 @@
         <v>628</v>
       </c>
       <c r="L555" t="s">
-        <v>1076</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="556" ht="13.8">
@@ -12166,7 +12376,7 @@
         <v>633</v>
       </c>
       <c r="L557" t="s">
-        <v>1077</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="558" ht="13.8">
@@ -12183,7 +12393,7 @@
         <v>636</v>
       </c>
       <c r="L558" t="s">
-        <v>1078</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="559" ht="13.8">
@@ -12200,7 +12410,7 @@
         <v>639</v>
       </c>
       <c r="L559" t="s">
-        <v>1079</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="560" ht="13.8">
@@ -12214,7 +12424,7 @@
         <v>641</v>
       </c>
       <c r="L560" t="s">
-        <v>1080</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="561" ht="23.85">
@@ -12231,7 +12441,7 @@
         <v>643</v>
       </c>
       <c r="L561" t="s">
-        <v>1081</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="562" ht="13.8">
@@ -12258,7 +12468,7 @@
         <v>645</v>
       </c>
       <c r="L563" t="s">
-        <v>1082</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="564" ht="23.85">
@@ -12275,7 +12485,7 @@
         <v>647</v>
       </c>
       <c r="L564" t="s">
-        <v>1083</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="565" ht="13.8">
@@ -12303,7 +12513,7 @@
         <v>649</v>
       </c>
       <c r="L566" t="s">
-        <v>1084</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="567" ht="23.85">
@@ -12320,7 +12530,7 @@
         <v>651</v>
       </c>
       <c r="L567" t="s">
-        <v>1085</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="568" ht="13.8">
@@ -12337,7 +12547,7 @@
         <v>654</v>
       </c>
       <c r="L568" t="s">
-        <v>1086</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="569" ht="13.8">
@@ -12365,7 +12575,7 @@
         <v>633</v>
       </c>
       <c r="L570" t="s">
-        <v>1077</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="571" ht="13.8">
@@ -12379,7 +12589,7 @@
         <v>656</v>
       </c>
       <c r="L571" t="s">
-        <v>1087</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="572" ht="23.85">
@@ -12393,7 +12603,7 @@
         <v>658</v>
       </c>
       <c r="L572" t="s">
-        <v>1088</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="573" ht="57.45">
@@ -12410,7 +12620,7 @@
         <v>660</v>
       </c>
       <c r="L573" t="s">
-        <v>1089</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="574" ht="13.8">
@@ -12424,7 +12634,7 @@
         <v>662</v>
       </c>
       <c r="L574" t="s">
-        <v>1090</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="575" ht="13.8">
@@ -12441,7 +12651,7 @@
         <v>664</v>
       </c>
       <c r="L575" t="s">
-        <v>1091</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="576" ht="23.85">
@@ -12458,7 +12668,7 @@
         <v>666</v>
       </c>
       <c r="L576" t="s">
-        <v>1092</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="577" ht="13.8">
@@ -12472,7 +12682,7 @@
         <v>668</v>
       </c>
       <c r="L577" t="s">
-        <v>1093</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="578" ht="13.8">
@@ -12489,7 +12699,7 @@
         <v>670</v>
       </c>
       <c r="L578" t="s">
-        <v>1094</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="579" ht="23.85">
@@ -12503,7 +12713,7 @@
         <v>672</v>
       </c>
       <c r="L579" t="s">
-        <v>1095</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="580" ht="13.8">
@@ -12520,7 +12730,7 @@
         <v>674</v>
       </c>
       <c r="L580" t="s">
-        <v>1096</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="581" ht="13.8">
@@ -12555,7 +12765,7 @@
         <v>676</v>
       </c>
       <c r="L583" t="s">
-        <v>1097</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="584" ht="13.8">
@@ -12569,7 +12779,7 @@
         <v>678</v>
       </c>
       <c r="L584" t="s">
-        <v>1098</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="585" ht="46.25">
@@ -12586,7 +12796,7 @@
         <v>680</v>
       </c>
       <c r="L585" t="s">
-        <v>1099</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="586" ht="23.85">
@@ -12601,7 +12811,7 @@
         <v>682</v>
       </c>
       <c r="L586" t="s">
-        <v>1100</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="587" ht="53.7">
@@ -12618,7 +12828,7 @@
         <v>684</v>
       </c>
       <c r="L587" t="s">
-        <v>1101</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="588" ht="64.15">
@@ -12635,7 +12845,7 @@
         <v>686</v>
       </c>
       <c r="L588" t="s">
-        <v>1102</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="589" ht="13.8">
@@ -12667,7 +12877,7 @@
         <v>688</v>
       </c>
       <c r="L590" t="s">
-        <v>1103</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="591" ht="13.8">
@@ -12697,7 +12907,7 @@
         <v>690</v>
       </c>
       <c r="L592" t="s">
-        <v>1104</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="593" ht="79.85">
@@ -12714,7 +12924,7 @@
         <v>692</v>
       </c>
       <c r="L593" t="s">
-        <v>1105</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="594" ht="13.8">
@@ -12742,7 +12952,7 @@
         <v>633</v>
       </c>
       <c r="L595" t="s">
-        <v>1106</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="596" ht="13.8">
@@ -12818,7 +13028,7 @@
         <v>695</v>
       </c>
       <c r="L605" t="s">
-        <v>1107</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="606" ht="13.8">
@@ -12849,7 +13059,7 @@
         <v>697</v>
       </c>
       <c r="L607" t="s">
-        <v>1108</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="608" ht="13.8">
@@ -12962,7 +13172,7 @@
         <v>704</v>
       </c>
       <c r="L623" t="s">
-        <v>1109</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="624" ht="13.8">
@@ -12980,7 +13190,7 @@
         <v>706</v>
       </c>
       <c r="L624" t="s">
-        <v>1110</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="625" ht="13.8">
@@ -12995,7 +13205,7 @@
         <v>708</v>
       </c>
       <c r="L625" t="s">
-        <v>1111</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="626" ht="13.8">
@@ -13013,7 +13223,7 @@
         <v>710</v>
       </c>
       <c r="L626" t="s">
-        <v>1112</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="627" ht="13.8">
@@ -13028,7 +13238,7 @@
         <v>712</v>
       </c>
       <c r="L627" t="s">
-        <v>1113</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="628" s="1" customFormat="1" ht="13.8">
@@ -13074,7 +13284,7 @@
         <v>706</v>
       </c>
       <c r="L630" t="s">
-        <v>1110</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="631" ht="13.4" customHeight="1">
@@ -13101,7 +13311,7 @@
         <v>715</v>
       </c>
       <c r="L632" t="s">
-        <v>1114</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="633" ht="13.8">
@@ -13119,7 +13329,7 @@
         <v>717</v>
       </c>
       <c r="L633" t="s">
-        <v>1115</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="634" ht="23.85">
@@ -13135,7 +13345,7 @@
         <v>719</v>
       </c>
       <c r="L634" t="s">
-        <v>1116</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="635" ht="13.8">
@@ -13155,7 +13365,7 @@
         <v>721</v>
       </c>
       <c r="L635" t="s">
-        <v>1117</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="636" ht="13.8">
@@ -13171,7 +13381,7 @@
         <v>723</v>
       </c>
       <c r="L636" t="s">
-        <v>1118</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="637" ht="13.8">
@@ -13195,7 +13405,7 @@
         <v>726</v>
       </c>
       <c r="L638" t="s">
-        <v>1119</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="639" ht="13.8">
@@ -13249,7 +13459,7 @@
         <v>728</v>
       </c>
       <c r="L641" t="s">
-        <v>1120</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="642" ht="13.8">
@@ -13285,7 +13495,7 @@
         <v>706</v>
       </c>
       <c r="L643" t="s">
-        <v>1110</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="644" ht="13.8">
@@ -13321,7 +13531,7 @@
         <v>730</v>
       </c>
       <c r="L645" t="s">
-        <v>1121</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="646" ht="13.8">
@@ -13350,7 +13560,7 @@
         <v>733</v>
       </c>
       <c r="L647" t="s">
-        <v>1122</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="648" ht="13.8">
@@ -13366,7 +13576,7 @@
         <v>735</v>
       </c>
       <c r="L648" t="s">
-        <v>1123</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="649" ht="13.8">
@@ -13382,7 +13592,7 @@
         <v>737</v>
       </c>
       <c r="L649" t="s">
-        <v>1124</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="650" ht="13.8">
@@ -13454,7 +13664,7 @@
         <v>741</v>
       </c>
       <c r="L659" t="s">
-        <v>1125</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="660" ht="13.8">
@@ -13471,7 +13681,7 @@
         <v>743</v>
       </c>
       <c r="L660" t="s">
-        <v>1126</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="661" ht="13.8">
@@ -13485,7 +13695,7 @@
         <v>745</v>
       </c>
       <c r="L661" t="s">
-        <v>1127</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="662" ht="13.8">
@@ -13502,7 +13712,7 @@
         <v>747</v>
       </c>
       <c r="L662" t="s">
-        <v>1128</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="663" ht="13.8">
@@ -13516,7 +13726,7 @@
         <v>749</v>
       </c>
       <c r="L663" t="s">
-        <v>1129</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="664" ht="74.6">
@@ -13533,7 +13743,7 @@
         <v>751</v>
       </c>
       <c r="L664" t="s">
-        <v>1130</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="665" ht="46.25">
@@ -13547,7 +13757,7 @@
         <v>753</v>
       </c>
       <c r="L665" t="s">
-        <v>1131</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="667" ht="12.8">
@@ -13604,7 +13814,7 @@
         <v>757</v>
       </c>
       <c r="L672" t="s">
-        <v>1132</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="673" ht="13.8">
@@ -13621,7 +13831,7 @@
         <v>759</v>
       </c>
       <c r="L673" t="s">
-        <v>1133</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="674" ht="13.8">
@@ -13638,7 +13848,7 @@
         <v>761</v>
       </c>
       <c r="L674" t="s">
-        <v>1134</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="675" ht="13.8">
@@ -13655,7 +13865,7 @@
         <v>763</v>
       </c>
       <c r="L675" t="s">
-        <v>1135</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="676" ht="13.8">
@@ -13669,7 +13879,7 @@
         <v>765</v>
       </c>
       <c r="L676" t="s">
-        <v>1136</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="677" ht="13.8">
@@ -13686,7 +13896,7 @@
         <v>767</v>
       </c>
       <c r="L677" t="s">
-        <v>1137</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="678" ht="13.8">
@@ -13700,7 +13910,7 @@
         <v>769</v>
       </c>
       <c r="L678" t="s">
-        <v>1138</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="679" ht="13.8">
@@ -13717,7 +13927,7 @@
         <v>771</v>
       </c>
       <c r="L679" t="s">
-        <v>1139</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="680" ht="13.8">
@@ -13731,7 +13941,7 @@
         <v>773</v>
       </c>
       <c r="L680" t="s">
-        <v>1140</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="681" ht="53.7">
@@ -13748,7 +13958,7 @@
         <v>775</v>
       </c>
       <c r="L681" t="s">
-        <v>1141</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="682" ht="13.8">
@@ -13762,7 +13972,7 @@
         <v>777</v>
       </c>
       <c r="L682" t="s">
-        <v>1142</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="683" ht="13.8">
@@ -13779,7 +13989,7 @@
         <v>779</v>
       </c>
       <c r="L683" t="s">
-        <v>1143</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="684" ht="57.45">
@@ -13796,7 +14006,7 @@
         <v>781</v>
       </c>
       <c r="L684" t="s">
-        <v>1144</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="685" ht="116.4">
@@ -13813,7 +14023,7 @@
         <v>783</v>
       </c>
       <c r="L685" t="s">
-        <v>1145</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="686" ht="57.45">
@@ -13830,7 +14040,7 @@
         <v>785</v>
       </c>
       <c r="L686" t="s">
-        <v>1146</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="687" ht="13.8">
@@ -13847,7 +14057,7 @@
         <v>787</v>
       </c>
       <c r="L687" t="s">
-        <v>1147</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="688" ht="13.8">
@@ -13867,7 +14077,7 @@
         <v>789</v>
       </c>
       <c r="L689" t="s">
-        <v>1148</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="690" ht="85.05">
@@ -13881,7 +14091,7 @@
         <v>791</v>
       </c>
       <c r="L690" t="s">
-        <v>1149</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="691" ht="13.8">
@@ -13898,7 +14108,7 @@
         <v>793</v>
       </c>
       <c r="L691" t="s">
-        <v>1150</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="692" ht="13.8">
@@ -13912,7 +14122,7 @@
         <v>795</v>
       </c>
       <c r="L692" t="s">
-        <v>1151</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="693" ht="13.8">
@@ -13929,7 +14139,7 @@
         <v>797</v>
       </c>
       <c r="L693" t="s">
-        <v>1152</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="694" ht="13.8">
@@ -13966,7 +14176,7 @@
         <v>799</v>
       </c>
       <c r="L696" t="s">
-        <v>1153</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="697" ht="13.8">
@@ -13980,7 +14190,7 @@
         <v>801</v>
       </c>
       <c r="L697" t="s">
-        <v>1154</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="698" ht="53.7">
@@ -13997,7 +14207,7 @@
         <v>803</v>
       </c>
       <c r="L698" t="s">
-        <v>1155</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="699" ht="13.8">
@@ -14014,7 +14224,7 @@
         <v>805</v>
       </c>
       <c r="L699" t="s">
-        <v>1156</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="700" ht="13.8">
@@ -14031,7 +14241,7 @@
         <v>807</v>
       </c>
       <c r="L700" t="s">
-        <v>1157</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="701" ht="13.8">
@@ -14045,7 +14255,7 @@
         <v>809</v>
       </c>
       <c r="L701" t="s">
-        <v>1158</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="702" ht="53.7">
@@ -14062,7 +14272,7 @@
         <v>811</v>
       </c>
       <c r="L702" t="s">
-        <v>1159</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="703" ht="13.8">
@@ -14084,8 +14294,593 @@
         <v>98</v>
       </c>
     </row>
+    <row r="711" ht="12.8">
+      <c r="A711" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="F711" s="1"/>
+    </row>
+    <row r="712" ht="12.8">
+      <c r="D712" s="4"/>
+      <c r="E712" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F712" s="13" t="s">
+        <v>814</v>
+      </c>
+      <c r="G712" s="4"/>
+    </row>
+    <row r="713" ht="12.8">
+      <c r="D713" s="4"/>
+      <c r="E713" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F713" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="G713" s="4"/>
+    </row>
+    <row r="714" ht="12.8">
+      <c r="D714" s="4"/>
+      <c r="E714" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="F714" s="4">
+        <v>2</v>
+      </c>
+      <c r="G714" s="4"/>
+    </row>
+    <row r="715" ht="12.8">
+      <c r="D715" s="4"/>
+      <c r="E715" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="F715" s="23" t="s">
+        <v>700</v>
+      </c>
+      <c r="G715" s="4"/>
+    </row>
+    <row r="716" ht="12.8">
+      <c r="D716" s="4"/>
+      <c r="E716" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F716" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="G716" s="4"/>
+    </row>
+    <row r="717" ht="12.8">
+      <c r="D717" s="4"/>
+      <c r="E717" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="F717" s="4">
+        <v>2</v>
+      </c>
+      <c r="G717" s="4"/>
+    </row>
+    <row r="718" ht="13.8">
+      <c r="F718" s="1"/>
+      <c r="J718" s="12"/>
+      <c r="K718" s="30"/>
+    </row>
+    <row r="719" ht="23.85">
+      <c r="F719" s="1"/>
+      <c r="I719" s="6">
+        <v>426</v>
+      </c>
+      <c r="J719" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="K719" s="8" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="720" ht="23.85">
+      <c r="F720" s="1"/>
+      <c r="I720" s="6">
+        <v>427</v>
+      </c>
+      <c r="J720" s="12" t="s">
+        <v>818</v>
+      </c>
+      <c r="K720" s="8" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="721" ht="49.95">
+      <c r="F721" s="1"/>
+      <c r="I721" s="6">
+        <v>428</v>
+      </c>
+      <c r="J721" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="K721" s="31" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="722" ht="13.8">
+      <c r="F722" s="1"/>
+      <c r="I722" s="6">
+        <v>429</v>
+      </c>
+      <c r="J722" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="K722" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="723" ht="49.95">
+      <c r="F723" s="1"/>
+      <c r="I723" s="6">
+        <v>430</v>
+      </c>
+      <c r="J723" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="K723" s="31" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="724" ht="13.8">
+      <c r="F724" s="1"/>
+      <c r="I724" s="6">
+        <v>431</v>
+      </c>
+      <c r="J724" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="K724" s="31" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="725" ht="13.8">
+      <c r="F725" s="1"/>
+      <c r="I725" s="6">
+        <v>432</v>
+      </c>
+      <c r="J725" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="K725" s="31" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="726" ht="13.8">
+      <c r="A726" s="4"/>
+      <c r="B726" s="4"/>
+      <c r="C726" s="4"/>
+      <c r="D726" s="4"/>
+      <c r="F726" s="1"/>
+      <c r="G726" s="4"/>
+      <c r="H726" s="4"/>
+      <c r="I726" s="6">
+        <v>433</v>
+      </c>
+      <c r="J726" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="K726" s="31" t="s">
+        <v>831</v>
+      </c>
+      <c r="L726" s="4"/>
+      <c r="M726" s="1"/>
+      <c r="N726" s="1"/>
+    </row>
+    <row r="727" ht="12.8">
+      <c r="D727" s="4"/>
+      <c r="E727" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="F727" s="4">
+        <v>2</v>
+      </c>
+      <c r="G727" s="4"/>
+    </row>
+    <row r="728" ht="12.8">
+      <c r="D728" s="4"/>
+      <c r="E728" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="F728" s="4">
+        <v>2</v>
+      </c>
+      <c r="G728" s="4"/>
+    </row>
+    <row r="729" ht="12.8">
+      <c r="D729" s="4"/>
+      <c r="E729" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F729" s="16" t="s">
+        <v>701</v>
+      </c>
+      <c r="G729" s="4"/>
+    </row>
+    <row r="730" ht="29.85">
+      <c r="A730" s="4"/>
+      <c r="B730" s="4"/>
+      <c r="C730" s="4"/>
+      <c r="D730" s="4"/>
+      <c r="F730" s="1"/>
+      <c r="G730" s="28" t="s">
+        <v>832</v>
+      </c>
+      <c r="H730" s="4"/>
+      <c r="I730" s="6">
+        <v>434</v>
+      </c>
+      <c r="J730" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="K730" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="L730" s="4"/>
+      <c r="M730" s="1"/>
+      <c r="N730" s="1"/>
+    </row>
+    <row r="731" ht="13.4" customHeight="1">
+      <c r="F731" s="1"/>
+      <c r="G731" s="28" t="s">
+        <v>832</v>
+      </c>
+      <c r="I731" s="6">
+        <v>435</v>
+      </c>
+      <c r="J731" s="12" t="s">
+        <v>833</v>
+      </c>
+      <c r="K731" s="4" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="732" ht="13.4" customHeight="1">
+      <c r="E732" s="4"/>
+      <c r="F732" s="16"/>
+      <c r="G732" s="26" t="s">
+        <v>832</v>
+      </c>
+      <c r="I732" s="6">
+        <v>436</v>
+      </c>
+      <c r="J732" s="12" t="s">
+        <v>835</v>
+      </c>
+      <c r="K732" s="8" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="733" ht="13.8">
+      <c r="F733" s="1"/>
+      <c r="G733" s="4"/>
+      <c r="I733" s="6">
+        <v>437</v>
+      </c>
+      <c r="J733" s="12" t="s">
+        <v>837</v>
+      </c>
+      <c r="K733" s="31" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="734" ht="29.85">
+      <c r="F734" s="1"/>
+      <c r="G734" s="28" t="s">
+        <v>832</v>
+      </c>
+      <c r="I734" s="6">
+        <v>438</v>
+      </c>
+      <c r="J734" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="K734" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="735" ht="29.85">
+      <c r="F735" s="1"/>
+      <c r="G735" s="28" t="s">
+        <v>832</v>
+      </c>
+      <c r="I735" s="6">
+        <v>439</v>
+      </c>
+      <c r="J735" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="K735" s="31" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="736" ht="29.85">
+      <c r="D736" s="4"/>
+      <c r="E736" s="4"/>
+      <c r="F736" s="1"/>
+      <c r="G736" s="28" t="s">
+        <v>832</v>
+      </c>
+      <c r="I736" s="6">
+        <v>440</v>
+      </c>
+      <c r="J736" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="K736" s="8" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="737" ht="13.8">
+      <c r="F737" s="1"/>
+      <c r="G737" s="4"/>
+      <c r="I737" s="6">
+        <v>441</v>
+      </c>
+      <c r="J737" s="12" t="s">
+        <v>845</v>
+      </c>
+      <c r="K737" s="31" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="738" ht="13.8">
+      <c r="F738" s="1"/>
+      <c r="G738" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="I738" s="6">
+        <v>442</v>
+      </c>
+      <c r="J738" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="K738" s="31" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="739" ht="13.8">
+      <c r="F739" s="1"/>
+      <c r="G739" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="I739" s="6">
+        <v>443</v>
+      </c>
+      <c r="J739" s="12" t="s">
+        <v>850</v>
+      </c>
+      <c r="K739" s="31" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="740" ht="13.8">
+      <c r="E740" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F740" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="I740" s="6"/>
+      <c r="J740" s="12"/>
+      <c r="K740" s="8"/>
+    </row>
+    <row r="741" ht="13.8">
+      <c r="F741" s="1"/>
+      <c r="G741" s="4"/>
+      <c r="I741" s="6">
+        <v>444</v>
+      </c>
+      <c r="J741" s="12" t="s">
+        <v>852</v>
+      </c>
+      <c r="K741" s="31" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="742" ht="13.8">
+      <c r="F742" s="1"/>
+      <c r="I742" s="6">
+        <v>445</v>
+      </c>
+      <c r="J742" s="12" t="s">
+        <v>854</v>
+      </c>
+      <c r="K742" s="31" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="743" ht="13.8">
+      <c r="E743" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F743" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="I743" s="6"/>
+      <c r="J743" s="12"/>
+      <c r="K743" s="8"/>
+    </row>
+    <row r="744" ht="59.7">
+      <c r="F744" s="1"/>
+      <c r="G744" s="4"/>
+      <c r="I744" s="6">
+        <v>446</v>
+      </c>
+      <c r="J744" s="15" t="s">
+        <v>856</v>
+      </c>
+      <c r="K744" s="31" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="745" ht="13.8">
+      <c r="F745" s="1"/>
+      <c r="G745" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I745" s="6">
+        <v>447</v>
+      </c>
+      <c r="J745" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="K745" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="746" ht="13.8">
+      <c r="F746" s="1"/>
+      <c r="G746" s="4"/>
+      <c r="I746" s="6">
+        <v>448</v>
+      </c>
+      <c r="J746" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="K746" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="747" ht="13.8">
+      <c r="F747" s="1"/>
+      <c r="G747" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I747" s="6">
+        <v>449</v>
+      </c>
+      <c r="J747" s="12" t="s">
+        <v>858</v>
+      </c>
+      <c r="K747" s="31" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="748" ht="13.8">
+      <c r="F748" s="1"/>
+      <c r="G748" s="4"/>
+      <c r="I748" s="6">
+        <v>450</v>
+      </c>
+      <c r="J748" s="12" t="s">
+        <v>860</v>
+      </c>
+      <c r="K748" s="8" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="749" ht="23.85">
+      <c r="F749" s="1"/>
+      <c r="G749" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I749" s="6">
+        <v>451</v>
+      </c>
+      <c r="J749" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="K749" s="8" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="750" ht="13.8">
+      <c r="F750" s="1"/>
+      <c r="G750" s="4"/>
+      <c r="I750" s="6">
+        <v>452</v>
+      </c>
+      <c r="J750" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="K750" s="31" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="751" ht="13.8">
+      <c r="F751" s="1"/>
+      <c r="G751" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I751" s="6">
+        <v>453</v>
+      </c>
+      <c r="J751" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="K751" s="31" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="752" ht="13.8">
+      <c r="F752" s="1"/>
+      <c r="G752" s="4"/>
+      <c r="I752" s="6">
+        <v>454</v>
+      </c>
+      <c r="J752" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="K752" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="753" ht="13.8">
+      <c r="F753" s="1"/>
+      <c r="G753" s="4"/>
+      <c r="I753" s="6">
+        <v>455</v>
+      </c>
+      <c r="J753" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="K753" s="31" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="754" ht="13.8">
+      <c r="F754" s="1"/>
+      <c r="G754" s="4"/>
+      <c r="I754" s="6"/>
+      <c r="J754" s="6"/>
+      <c r="K754" s="8"/>
+    </row>
+    <row r="755" ht="13.8">
+      <c r="E755" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F755" s="1">
+        <v>3</v>
+      </c>
+      <c r="J755" s="6"/>
+      <c r="K755" s="6"/>
+    </row>
+    <row r="756" ht="12.8">
+      <c r="E756" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F756" s="1"/>
+    </row>
+    <row r="757" ht="12.8">
+      <c r="E757" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F757" s="1" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="758" ht="12.8">
+      <c r="E758" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F758" s="1"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="I108:I339 I4:I106 J656 J615:J619 J650:J651 J623 J637 I658:I1048576 I611:I614 I341:I553 J547:J550 I599:I601 J599 I597:J598 I616:I656">
+  <conditionalFormatting sqref="I108:I339 I4:I106 J656 J615:J619 J650:J651 J623 J637 I611:I614 I341:I553 J547:J550 I599:I601 J599 I597:J598 I616:I656 J712:J715 J730:J754 I658:I1048576 J719:J727">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I602:I610 I564:I596 I554:I561">
